--- a/results/monthly_investor_report_2026-08-13.xlsx
+++ b/results/monthly_investor_report_2026-08-13.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1568,7 +1568,7 @@
         <v>0.0439164979259993</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.1382006157766129</v>
+        <v>0.138200615776613</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>370.0262375089882</v>
@@ -1682,7 +1682,7 @@
         <v>0.0060687804495014</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>0.07305447787943251</v>
+        <v>0.0730544778794326</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>365.9026706205821</v>
@@ -1691,7 +1691,7 @@
         <v>378.7848958392373</v>
       </c>
       <c r="J12" s="19" t="n">
-        <v>404.0050109216063</v>
+        <v>404.0050109216064</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>357.675</v>
@@ -1736,7 +1736,7 @@
         <v>-0.0789866180022725</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0105208185445254</v>
+        <v>-0.0105208185445256</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>0.0584958172872285</v>
@@ -1745,7 +1745,7 @@
         <v>17.32426122350304</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>18.61210287473859</v>
+        <v>18.61210287473858</v>
       </c>
       <c r="J13" s="22" t="n">
         <v>19.91030575787502</v>
@@ -1961,22 +1961,22 @@
         <v>69.05000305175781</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>0.0306243693277838</v>
+        <v>0.0306243693277841</v>
       </c>
       <c r="F17" s="17" t="n">
         <v>0.1086638342048738</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.1743487455946222</v>
+        <v>0.1743487455946224</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>71.16461584729944</v>
+        <v>71.16461584729946</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>76.55324113522005</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>81.08878446713662</v>
+        <v>81.08878446713663</v>
       </c>
       <c r="K17" s="16" t="n">
         <v>65.05111663722695</v>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="E5" s="20" t="n">
-        <v>0.0591312790793305</v>
+        <v>0.0591312790793308</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>-0.0102689785012989</v>
+        <v>-0.0102689785012987</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>0.0123804463255767</v>
+        <v>0.0123804463255772</v>
       </c>
       <c r="H5" s="20" t="n">
         <v>0.2481088749818165</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="J5" s="20" t="n">
-        <v>0.0217091481717317</v>
+        <v>0.0217091481717316</v>
       </c>
       <c r="K5" s="20" t="n">
         <v>0.0371204201966619</v>
@@ -2374,7 +2374,7 @@
         <v>0.0270933955942019</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>-0.0105208185445254</v>
+        <v>-0.0105208185445256</v>
       </c>
     </row>
     <row r="10">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="J10" s="20" t="n">
-        <v>0.0217785131066505</v>
+        <v>0.0217785131066506</v>
       </c>
       <c r="K10" s="20" t="n">
         <v>0.0292262535427767</v>
@@ -2572,7 +2572,7 @@
         <v>-0.0187844966656595</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.0672268287987855</v>
+        <v>-0.0672268287987856</v>
       </c>
       <c r="G14" s="25" t="n">
         <v>-0.1447712328733906</v>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="E16" s="25" t="n">
-        <v>-0.0644283000974651</v>
+        <v>-0.0644283000974652</v>
       </c>
       <c r="F16" s="25" t="n">
         <v>-0.09956333210374591</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E17" s="25" t="n">
-        <v>-0.0449541090153023</v>
+        <v>-0.0449541090153021</v>
       </c>
       <c r="F17" s="25" t="n">
         <v>-0.1395106937258488</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="J17" s="25" t="n">
-        <v>0.0218911391981522</v>
+        <v>0.0218911391981521</v>
       </c>
       <c r="K17" s="25" t="n">
         <v>0.0236686907772818</v>
@@ -2830,10 +2830,10 @@
         <v>-0.0429726990336588</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.1748038008354153</v>
+        <v>-0.1748038008354154</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.2409783172235023</v>
+        <v>-0.2409783172235025</v>
       </c>
       <c r="H20" s="25" t="n">
         <v>-0.1458254589228474</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.0152227377417771</v>
+        <v>0.0152227377417772</v>
       </c>
       <c r="K20" s="25" t="n">
         <v>0.0649744697948437</v>
@@ -2880,7 +2880,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2999,7 +2999,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3375,7 +3375,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3506,7 +3506,7 @@
         <v>202.3999938964844</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>0.02741113653037752</v>
+        <v>0.02741113653037774</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>79666.21246549161</v>

--- a/results/monthly_investor_report_2026-08-13.xlsx
+++ b/results/monthly_investor_report_2026-08-13.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2880,7 +2880,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2999,7 +2999,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3375,7 +3375,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
